--- a/GameConfig/bullet.xlsx
+++ b/GameConfig/bullet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,13 +63,6 @@
   <si>
     <t>bulletPath</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bullets/NormalBullet_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bullets/NormalBullet_002</t>
   </si>
   <si>
     <r>
@@ -100,6 +93,19 @@
 (支持 float string int bool 数组float[] string[] int[] bool[] 数组值用(;)分割)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullet_89003</t>
+  </si>
+  <si>
+    <t>Bullet/Bullet_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bullet/Bullet_2</t>
+  </si>
+  <si>
+    <t>Bullet/Bullet_3</t>
   </si>
 </sst>
 </file>
@@ -639,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.75" style="3" customWidth="1"/>
@@ -678,7 +684,7 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -686,7 +692,15 @@
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -717,7 +731,7 @@
     </row>
     <row r="3" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">

--- a/GameConfig/bullet.xlsx
+++ b/GameConfig/bullet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,6 +106,18 @@
   </si>
   <si>
     <t>Bullet/Bullet_3</t>
+  </si>
+  <si>
+    <t>effect_248011</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exploAudioId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>炮弹爆炸音效Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -645,62 +657,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.75" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1"/>
-    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="2" max="3" width="21.875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="6" max="6" width="13.75" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C2" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
